--- a/extenbooks/S511.xlsx
+++ b/extenbooks/S511.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=share</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=share</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BLS CES, units=share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S511-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S511-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S511-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>0.57</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>0.5649999999999999</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>0.5600000000000001</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>0.555</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>0.55</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>0.545</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>0.54</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>0.535</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>0.53</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>0.525</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>0.52</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>0.519</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>0.518</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>0.517</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>0.516</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>0.514</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>0.513</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>0.512</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,13 +759,25 @@
       <c r="B21" s="3" t="n">
         <v>0.511</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
         <v>1967</v>
       </c>
       <c r="B22" s="3" t="n">
-        <v>0.51</v>
+        <v>0.44</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>0.509</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>0.508</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -661,6 +815,12 @@
       <c r="B25" s="3" t="n">
         <v>0.507</v>
       </c>
+      <c r="C25" s="3" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -669,6 +829,12 @@
       <c r="B26" s="3" t="n">
         <v>0.506</v>
       </c>
+      <c r="C26" s="3" t="n">
+        <v>0.506</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -677,6 +843,12 @@
       <c r="B27" s="3" t="n">
         <v>0.505</v>
       </c>
+      <c r="C27" s="3" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -685,6 +857,12 @@
       <c r="B28" s="3" t="n">
         <v>0.504</v>
       </c>
+      <c r="C28" s="3" t="n">
+        <v>0.504</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -693,6 +871,12 @@
       <c r="B29" s="3" t="n">
         <v>0.503</v>
       </c>
+      <c r="C29" s="3" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -701,6 +885,12 @@
       <c r="B30" s="3" t="n">
         <v>0.502</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -709,6 +899,12 @@
       <c r="B31" s="3" t="n">
         <v>0.501</v>
       </c>
+      <c r="C31" s="3" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -717,6 +913,12 @@
       <c r="B32" s="3" t="n">
         <v>0.5</v>
       </c>
+      <c r="C32" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -725,6 +927,12 @@
       <c r="B33" s="3" t="n">
         <v>0.488</v>
       </c>
+      <c r="C33" s="3" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -733,6 +941,12 @@
       <c r="B34" s="3" t="n">
         <v>0.477</v>
       </c>
+      <c r="C34" s="3" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -741,6 +955,12 @@
       <c r="B35" s="3" t="n">
         <v>0.465</v>
       </c>
+      <c r="C35" s="3" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -749,6 +969,12 @@
       <c r="B36" s="3" t="n">
         <v>0.453</v>
       </c>
+      <c r="C36" s="3" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -757,6 +983,12 @@
       <c r="B37" s="3" t="n">
         <v>0.442</v>
       </c>
+      <c r="C37" s="3" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -765,6 +997,12 @@
       <c r="B38" s="3" t="n">
         <v>0.43</v>
       </c>
+      <c r="C38" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -773,6 +1011,12 @@
       <c r="B39" s="3" t="n">
         <v>0.418</v>
       </c>
+      <c r="C39" s="3" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -781,6 +1025,12 @@
       <c r="B40" s="3" t="n">
         <v>0.407</v>
       </c>
+      <c r="C40" s="3" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -789,6 +1039,12 @@
       <c r="B41" s="3" t="n">
         <v>0.395</v>
       </c>
+      <c r="C41" s="3" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -797,6 +1053,12 @@
       <c r="B42" s="3" t="n">
         <v>0.383</v>
       </c>
+      <c r="C42" s="3" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -805,6 +1067,12 @@
       <c r="B43" s="3" t="n">
         <v>0.372</v>
       </c>
+      <c r="C43" s="3" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -812,6 +1080,502 @@
       </c>
       <c r="B44" s="3" t="n">
         <v>0.36</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0.3549653198090102</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0.3549653198090102</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0.3467669606671567</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0.3467669606671567</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0.3431267933154553</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0.3431267933154553</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.3415059738576416</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.3415059738576416</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>0.3414955307082922</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>0.3414955307082922</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0.3397963310277366</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0.3397963310277366</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0.3375371187025012</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0.3375371187025012</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0.3362446880637173</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0.3362446880637173</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0.3343968595443526</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0.3343968595443526</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0.3307481554401764</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0.3307481554401764</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>0.3282297557146672</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>0.3282297557146672</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0.3222584059523595</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0.3222584059523595</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0.3151199455738788</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0.3151199455738788</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0.3095527399019459</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0.3095527399019459</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0.3084979832482704</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0.3084979832482704</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0.3087237435853338</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0.3087237435853338</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.3095373251189405</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0.3095373251189405</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0.3065384010696235</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>0.3065384010696235</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>0.3018532811268752</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0.3018532811268752</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0.287989025653724</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.287989025653724</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0.2832469421158249</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0.2832469421158249</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0.2831935701105252</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0.2831935701105252</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0.2831569420564349</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.2831569420564349</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.2824754791933436</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.2824754791933436</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0.2831352988707836</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.2831352988707836</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0.2827605448868994</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0.2827605448868994</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0.2811162151129498</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.2811162151129498</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0.280978407816415</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0.280978407816415</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0.2823669726237893</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0.2823669726237893</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0.2822081234731446</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0.2822081234731446</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0.2829304192619705</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.2829304192619705</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>0.281312505977855</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>0.281312505977855</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0.2811432917612408</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0.2811432917612408</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0.2806746303046729</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0.2806746303046729</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0.2794513450201996</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0.2794513450201996</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +1589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +1688,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -948,7 +1712,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_2, Fig_5_7, Fig_9_3</t>
+          <t>Fig_5_2, Fig_5_7, Fig_9_3, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -990,386 +1754,391 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S511-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S511-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BLS CES</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S511-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S511 — Productive Labor Share (Lp/L)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix 5.7</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: share</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+          <t># S511 — Productive Labor Share (Lp/L)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: time_series</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix 5.7</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Units**: share</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Productive Labor Share (Lp/L). The share of total employment classified as productive. Falls secularly 1948-1989 from 0.57 to 0.36.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Productive Labor Share (Lp/L). The share of total employment classified as productive. Falls secularly 1948-1989 from 0.57 to 0.36.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>| `S511-A` | S&amp;T 1994 | 1948-1989 | share |</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>| `S511-EXT` | BLS CES | 1990-2024 | share |</t>
+          <t>## Subseries</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>| `S511-COMBINED` |  | 1948-2024 | share |</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>| Subseries | Source | Period | Units |</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>| `S511-A` | S&amp;T 1994 | 1948-1989 | share |</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>| `S511-EXT` | BLS CES | 1990-2024 | share |</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>| `S511-COMBINED` |  | 1948-2024 | share |</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>### S511-A (book period, 1948-1989)</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1. Read `data/source/book_tables/Table5_7_KeyRatios.csv`.</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2. Extract column `T511A` (book-authoritative values; the `T511` column without the A-suffix is the replicator-recomputed comparison and is not used here).</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>### S511-A (book period, 1948-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Validator checks the loaded series against the published benchmark years from validation_config.json.</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1. Read `data/source/book_tables/Table5_7_KeyRatios.csv`.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>2. Extract column `T511A` (book-authoritative values; the `T511` column without the A-suffix is the replicator-recomputed comparison and is not used here).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3. No further transformation — this is the canonical published value.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Validator checks the loaded series against the published benchmark years from validation_config.json.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1948=0.57, 1958=0.52, 1967=0.51, 1977=0.50, 1989=0.36</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Tolerance class: `share_series` (rel 0.05 / abs 0.02).</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S511_productive_labor_share.py` writes to `data/intermediate/validation/S511.json`.</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1948=0.57, 1958=0.52, 1967=0.51, 1977=0.50, 1989=0.36</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tolerance class: `share_series` (rel 0.05 / abs 0.02).</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S511_productive_labor_share.py` writes to `data/intermediate/validation/S511.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>data/source/book_tables/Table5_7_KeyRatios.csv</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S511_productive_labor_share.py</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S511.csv</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S511_productive_labor_share.py</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S511.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1377,7 +2146,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S511_productive_labor_share.py</t>
+          <t>data/source/book_tables/Table5_7_KeyRatios.csv</t>
         </is>
       </c>
     </row>
@@ -1385,65 +2154,105 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S511_productive_labor_share.py</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S511.csv</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>---</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S511_productive_labor_share.py</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S511.csv</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S511_productive_labor_share.py</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Table 5.7 (Key Ratios), Chapter 5.</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Table 5.7 (Key Ratios), Chapter 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1460,10 +2269,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1488,263 +2297,393 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Lp/L = productive employment divided by total employment. Productive sectors are classified per the 85 IO sector concordance. Employment decomposition specifics: Agriculture uses (Lp/L)_min × L_agr; Government enterprises uses (Lp/L)_nongovtot × L_ge; Trade is entirely unproductive; FIRE is decomposed into fi/re/br/gr subsectors.</t>
+          <t>(Lp)_j = (Lp/L)_j · (L_j) = estimated production worker employment in the jth production sector; Lp = ∑ (Lp)_j = total productive labor; Lu = L − Lp = total unproductive labor.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>benchmark_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Book benchmarks from Table 5.7: 1948=0.57, 1958=0.52, 1967=0.51, 1977=0.50, 1989=0.36. The sharp decline from 0.50 to 0.36 between 1977 and 1989 reflects deindustrialization and the shift to services.</t>
+          <t>Productive labor is the production labor employed in capitalist production sectors: agriculture, mining, construction, transportation and public utilities, manufacturing, and productive services (defined as all services except business services, legal services, and private households, as in Table E.1).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.7; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Book period from Table E.3 (Appendix E, chunk_31). Extension via BLS Current Employment Statistics (CES) production worker data as a proxy for productive labor share. BLS CES provides production/nonsupervisory worker counts by industry.</t>
+          <t>V*/W declines by 34%, while Lp/L declines by 37%.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_31/full_transcription.md; BLS CES</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fig 5.2 shows the secular decline in productive labor share. Fig 5.7 decomposes employment into productive and unproductive components. Fig 9.3 connects Lp/L to the profit rate decomposition.</t>
+          <t>Lp/L, 44%, -37%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Figs 5.2, 5.7, 9.3; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>external_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mohun decomposes unproductive labor into Luw (unproductive wage workers) and Lum (unproductive management). His broader productive classification yields a higher Lp/L. See mohun_unproductive_decomposition*.csv and mohun_employment*.csv for comparison data.</t>
+          <t>Productive Labor (Lp): 33,000 (1948) → ~41,000 (1988); Total Labor (L): ~58,000 (1948) → &gt;110,000 (1988); Lp/L ratio: Declined by more than 37% over postwar period (Figure 5.9); Lu/Lp ratio: Rose sharply by almost 138% over same period (Figure 5.11)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>employment_decomposition</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Special sector rules: Agriculture productive share uses mining sector ratio (Lp/L)_min as proxy. Government enterprises use non-government total ratio. All trade employment is unproductive. FIRE sectors decomposed: finance/insurance partially productive (brokers, some banking), real estate entirely unproductive.</t>
+          <t>Lp/L = productive employment divided by total employment. Productive sectors are classified per the 85 IO sector concordance. Employment decomposition specifics: Agriculture uses (Lp/L)_min × L_agr; Government enterprises uses (Lp/L)_nongovtot × L_ge; Trade is entirely unproductive; FIRE is decomposed into fi/re/br/gr subsectors.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_27/full_transcription.md</t>
+          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_15/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>benchmark_values</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BLS CES production worker classification does not perfectly match ST's theoretical productive/unproductive distinction. CES 'production workers' includes some supervisory roles in goods-producing sectors and excludes some productive workers in mixed sectors.</t>
+          <t>Book benchmarks from Table 5.7: 1948=0.57, 1958=0.52, 1967=0.51, 1977=0.50, 1989=0.36. The sharp decline from 0.50 to 0.36 between 1977 and 1989 reflects deindustrialization and the shift to services.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DPR T511_DPR.md; EPR T511_EPR.md</t>
+          <t>ST_1994, Table 5.7; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>data_source</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DEC-005: BLS CES production/nonsupervisory worker ratios are used as the proxy for IO-based productive/unproductive labor decomposition in the extension period. S511 extension is certified at 78% faithfulness (CERTIFIED WITH NOTES). Cross-validated against Mohun (2005) estimates.</t>
+          <t>Book period from Table E.3 (Appendix E, chunk_31). Extension via BLS Current Employment Statistics (CES) production worker data as a proxy for productive labor share. BLS CES provides production/nonsupervisory worker counts by industry.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md#DEC-005</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_31/full_transcription.md; BLS CES</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Fig 5.2 shows the secular decline in productive labor share. Fig 5.7 decomposes employment into productive and unproductive components. Fig 9.3 connects Lp/L to the profit rate decomposition.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Figs 5.2, 5.7, 9.3; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_13/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>external_comparison</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Productive labor share Lp/L declines from 0.57 (1948) to 0.36 (1989). Employment decomposition uses sector-specific rules for agriculture, government enterprises, trade, and FIRE. Extended via BLS CES production worker data (DEC-005, faithfulness 78%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
+          <t>Mohun decomposes unproductive labor into Luw (unproductive wage workers) and Lum (unproductive management). His broader productive classification yields a higher Lp/L. See mohun_unproductive_decomposition*.csv and mohun_employment*.csv for comparison data.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Mohun_2013; Inputs/ExternalSources/Mohun/</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>employment_decomposition</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Special sector rules: Agriculture productive share uses mining sector ratio (Lp/L)_min as proxy. Government enterprises use non-government total ratio. All trade employment is unproductive. FIRE sectors decomposed: finance/insurance partially productive (brokers, some banking), real estate entirely unproductive.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_27/full_transcription.md</t>
+        </is>
+      </c>
+    </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>caveat</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>BLS CES production worker classification does not perfectly match ST's theoretical productive/unproductive distinction. CES 'production workers' includes some supervisory roles in goods-producing sectors and excludes some productive workers in mixed sectors.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>DPR T511_DPR.md; EPR T511_EPR.md</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BLS CES production worker ≠ ST's theoretical productive worker</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Agriculture and government enterprise proxy ratios introduce approximation</t>
-        </is>
-      </c>
-    </row>
+          <t>[internal-decision-record]: BLS CES production/nonsupervisory worker ratios are used as the proxy for IO-based productive/unproductive labor decomposition in the extension period. S511 extension is certified at 78% faithfulness (CERTIFIED WITH NOTES). Cross-validated against Mohun (2005) estimates.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[internal-decision-log]#[internal-decision-record]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1977-1989 decline is very sharp — may reflect classification discontinuity</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>109</v>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S504</t>
-        </is>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>113</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S512</t>
-        </is>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>S515</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>S516</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Productive labor share Lp/L declines from 0.57 (1948) to 0.36 (1989). Employment decomposition uses sector-specific rules for agriculture, government enterprises, trade, and FIRE. Extended via BLS CES production worker data ([internal-decision-record], faithfulness 78%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>BLS CES production worker ≠ ST's theoretical productive worker</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Agriculture and government enterprise proxy ratios introduce approximation</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1977-1989 decline is very sharp — may reflect classification discontinuity</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S504</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S512</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S515</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>S516</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>BLS_CES</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Bureau of Labor Statistics. Current Employment Statistics (CES). https://www.bls.gov/ces/</t>
         </is>
@@ -1761,11 +2700,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="17" customWidth="1" min="5" max="5"/>
@@ -1857,91 +2796,226 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>level</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S511-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S511-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"1948": 0.57, "1967": 0.48, "1989": 0.37}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.7 column Lp/L (productive labor share); Appendix E.3 (productive employment); identity Lp/L", "shaikh_appendix_ref": "Table 5.7 (Lp/L, 1948-1989); Appendix E.3 (productive employment by sector); cf. Figure 5.7", "extension_source": "BLS CES (Current Employment Statistics) industry-level employment data, aggregated through the productive/unproductive concordance to compute Lp and L", "extension_url": "https://www.bls.gov/ces/", "conceptual_continuity": "Productive labor share Lp/L is the fraction of total employment classified as productive under the book's Appendix C concordance. The construct is directly observable in BLS CES employment by industry, subject to applying the productive/unproductive partition. Conceptual continuity holds if Appendix C is faithfully updated for post-1997 NAICS industries; otherwise the partition drifts.", "vintage_note": "BLS CES underwent the 2003 establishment-survey overhaul (NAICS-based industry classification, reweighted sample). Pre-2003 SIC-based employment levels are not directly comparable. Productive/unproductive partition must be updated for NAICS industries (information sector, professional/business services).", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1948": 0.57, "1958": 0.52, "1967": 0.44, "1977": 0.5, "1989": 0.36}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[0.1, 0.8]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>share_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>source_table</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Table 5.14, p.140</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>previous_1967_value</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>previous_1967_source</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>code-derived (pre-v1.0, linear interpolation in Table5_7_KeyRatios.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1967 midpoint anchor corrected from code-derived 0.51 to book Table 5.14 value 0.44. Endpoints 1948/1989 preserved from Table 5.7. Drift documented in DIV-006. Note: 1958/1977 intermediate values remain code-derived linear interpolations from Table 5.7 source CSV; only the 1967 midpoint has a directly-quoted book anchor in Table 5.14 (p.140).</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S511.xlsx
+++ b/extenbooks/S511.xlsx
@@ -519,10 +519,10 @@
         <v>1949</v>
       </c>
       <c r="B4" s="3" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.55</v>
       </c>
       <c r="D4" s="3" t="n">
         <v/>
@@ -533,10 +533,10 @@
         <v>1950</v>
       </c>
       <c r="B5" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="D5" s="3" t="n">
         <v/>
@@ -547,10 +547,10 @@
         <v>1951</v>
       </c>
       <c r="B6" s="3" t="n">
-        <v>0.555</v>
+        <v>0.53</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>0.555</v>
+        <v>0.53</v>
       </c>
       <c r="D6" s="3" t="n">
         <v/>
@@ -561,10 +561,10 @@
         <v>1952</v>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="D7" s="3" t="n">
         <v/>
@@ -575,10 +575,10 @@
         <v>1953</v>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.545</v>
+        <v>0.51</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>0.545</v>
+        <v>0.51</v>
       </c>
       <c r="D8" s="3" t="n">
         <v/>
@@ -589,10 +589,10 @@
         <v>1954</v>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="D9" s="3" t="n">
         <v/>
@@ -603,10 +603,10 @@
         <v>1955</v>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.535</v>
+        <v>0.5</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.535</v>
+        <v>0.5</v>
       </c>
       <c r="D10" s="3" t="n">
         <v/>
@@ -617,10 +617,10 @@
         <v>1956</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
       <c r="D11" s="3" t="n">
         <v/>
@@ -631,10 +631,10 @@
         <v>1957</v>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0.525</v>
+        <v>0.49</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.525</v>
+        <v>0.49</v>
       </c>
       <c r="D12" s="3" t="n">
         <v/>
@@ -645,10 +645,10 @@
         <v>1958</v>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0.52</v>
+        <v>0.47</v>
       </c>
       <c r="D13" s="3" t="n">
         <v/>
@@ -659,10 +659,10 @@
         <v>1959</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>0.519</v>
+        <v>0.47</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.519</v>
+        <v>0.47</v>
       </c>
       <c r="D14" s="3" t="n">
         <v/>
@@ -673,10 +673,10 @@
         <v>1960</v>
       </c>
       <c r="B15" s="3" t="n">
-        <v>0.518</v>
+        <v>0.46</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.518</v>
+        <v>0.46</v>
       </c>
       <c r="D15" s="3" t="n">
         <v/>
@@ -687,10 +687,10 @@
         <v>1961</v>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.517</v>
+        <v>0.45</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.517</v>
+        <v>0.45</v>
       </c>
       <c r="D16" s="3" t="n">
         <v/>
@@ -701,10 +701,10 @@
         <v>1962</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0.516</v>
+        <v>0.45</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0.516</v>
+        <v>0.45</v>
       </c>
       <c r="D17" s="3" t="n">
         <v/>
@@ -715,10 +715,10 @@
         <v>1963</v>
       </c>
       <c r="B18" s="3" t="n">
-        <v>0.514</v>
+        <v>0.45</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.514</v>
+        <v>0.45</v>
       </c>
       <c r="D18" s="3" t="n">
         <v/>
@@ -729,10 +729,10 @@
         <v>1964</v>
       </c>
       <c r="B19" s="3" t="n">
-        <v>0.513</v>
+        <v>0.45</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.513</v>
+        <v>0.45</v>
       </c>
       <c r="D19" s="3" t="n">
         <v/>
@@ -743,10 +743,10 @@
         <v>1965</v>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.512</v>
+        <v>0.45</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.512</v>
+        <v>0.45</v>
       </c>
       <c r="D20" s="3" t="n">
         <v/>
@@ -757,10 +757,10 @@
         <v>1966</v>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0.511</v>
+        <v>0.44</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.511</v>
+        <v>0.44</v>
       </c>
       <c r="D21" s="3" t="n">
         <v/>
@@ -785,10 +785,10 @@
         <v>1968</v>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.509</v>
+        <v>0.43</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.509</v>
+        <v>0.43</v>
       </c>
       <c r="D23" s="3" t="n">
         <v/>
@@ -799,10 +799,10 @@
         <v>1969</v>
       </c>
       <c r="B24" s="3" t="n">
-        <v>0.508</v>
+        <v>0.43</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.508</v>
+        <v>0.43</v>
       </c>
       <c r="D24" s="3" t="n">
         <v/>
@@ -813,10 +813,10 @@
         <v>1970</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0.507</v>
+        <v>0.42</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.507</v>
+        <v>0.42</v>
       </c>
       <c r="D25" s="3" t="n">
         <v/>
@@ -827,10 +827,10 @@
         <v>1971</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0.506</v>
+        <v>0.42</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.506</v>
+        <v>0.42</v>
       </c>
       <c r="D26" s="3" t="n">
         <v/>
@@ -841,10 +841,10 @@
         <v>1972</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.505</v>
+        <v>0.42</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.505</v>
+        <v>0.42</v>
       </c>
       <c r="D27" s="3" t="n">
         <v/>
@@ -855,10 +855,10 @@
         <v>1973</v>
       </c>
       <c r="B28" s="3" t="n">
-        <v>0.504</v>
+        <v>0.43</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.504</v>
+        <v>0.43</v>
       </c>
       <c r="D28" s="3" t="n">
         <v/>
@@ -869,10 +869,10 @@
         <v>1974</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.503</v>
+        <v>0.42</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.503</v>
+        <v>0.42</v>
       </c>
       <c r="D29" s="3" t="n">
         <v/>
@@ -883,10 +883,10 @@
         <v>1975</v>
       </c>
       <c r="B30" s="3" t="n">
-        <v>0.502</v>
+        <v>0.41</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.502</v>
+        <v>0.41</v>
       </c>
       <c r="D30" s="3" t="n">
         <v/>
@@ -897,10 +897,10 @@
         <v>1976</v>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0.501</v>
+        <v>0.41</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.501</v>
+        <v>0.41</v>
       </c>
       <c r="D31" s="3" t="n">
         <v/>
@@ -911,10 +911,10 @@
         <v>1977</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.5</v>
+        <v>0.41</v>
       </c>
       <c r="D32" s="3" t="n">
         <v/>
@@ -925,10 +925,10 @@
         <v>1978</v>
       </c>
       <c r="B33" s="3" t="n">
-        <v>0.488</v>
+        <v>0.41</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>0.488</v>
+        <v>0.41</v>
       </c>
       <c r="D33" s="3" t="n">
         <v/>
@@ -939,10 +939,10 @@
         <v>1979</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0.477</v>
+        <v>0.4</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0.477</v>
+        <v>0.4</v>
       </c>
       <c r="D34" s="3" t="n">
         <v/>
@@ -953,10 +953,10 @@
         <v>1980</v>
       </c>
       <c r="B35" s="3" t="n">
-        <v>0.465</v>
+        <v>0.4</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>0.465</v>
+        <v>0.4</v>
       </c>
       <c r="D35" s="3" t="n">
         <v/>
@@ -967,10 +967,10 @@
         <v>1981</v>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.453</v>
+        <v>0.39</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.453</v>
+        <v>0.39</v>
       </c>
       <c r="D36" s="3" t="n">
         <v/>
@@ -981,10 +981,10 @@
         <v>1982</v>
       </c>
       <c r="B37" s="3" t="n">
-        <v>0.442</v>
+        <v>0.38</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0.442</v>
+        <v>0.38</v>
       </c>
       <c r="D37" s="3" t="n">
         <v/>
@@ -995,10 +995,10 @@
         <v>1983</v>
       </c>
       <c r="B38" s="3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="D38" s="3" t="n">
         <v/>
@@ -1009,10 +1009,10 @@
         <v>1984</v>
       </c>
       <c r="B39" s="3" t="n">
-        <v>0.418</v>
+        <v>0.38</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>0.418</v>
+        <v>0.38</v>
       </c>
       <c r="D39" s="3" t="n">
         <v/>
@@ -1023,10 +1023,10 @@
         <v>1985</v>
       </c>
       <c r="B40" s="3" t="n">
-        <v>0.407</v>
+        <v>0.37</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.407</v>
+        <v>0.37</v>
       </c>
       <c r="D40" s="3" t="n">
         <v/>
@@ -1037,10 +1037,10 @@
         <v>1986</v>
       </c>
       <c r="B41" s="3" t="n">
-        <v>0.395</v>
+        <v>0.37</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.395</v>
+        <v>0.37</v>
       </c>
       <c r="D41" s="3" t="n">
         <v/>
@@ -1051,10 +1051,10 @@
         <v>1987</v>
       </c>
       <c r="B42" s="3" t="n">
-        <v>0.383</v>
+        <v>0.36</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>0.383</v>
+        <v>0.36</v>
       </c>
       <c r="D42" s="3" t="n">
         <v/>
@@ -1065,10 +1065,10 @@
         <v>1988</v>
       </c>
       <c r="B43" s="3" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="D43" s="3" t="n">
         <v/>
@@ -2404,12 +2404,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Book benchmarks from Table 5.7: 1948=0.57, 1958=0.52, 1967=0.51, 1977=0.50, 1989=0.36. The sharp decline from 0.50 to 0.36 between 1977 and 1989 reflects deindustrialization and the shift to services.</t>
+          <t>Book benchmarks from Table 5.5 (Total labor and productive employment, 1948-89, p.110): Lp/L = 0.57 (1948), 0.47 (1958), 0.44 (1967), 0.41 (1977), 0.36 (1989). The series declines secularly across the whole postwar period (not just 1977-89). CORRECTION 2026-06-11: an earlier version of this entry listed 1958=0.52/1967=0.51/1977=0.50 citing 'Table 5.7'; those values do not appear in the book. The canonical Lp/L row is in Table 5.5, and the typical 1967 relative level in Table 5.14 (p.151) is 44% with a -37% change over 1948-89 — both consistent with the registry reference_values.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.7; Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_16/full_transcription.md</t>
+          <t>ST_1994, Table 5.5 p.110 (PDF p.130); Table 5.14 p.151</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>140</v>
+        <v>151</v>
       </c>
     </row>
     <row r="21">
@@ -2700,7 +2700,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2907,38 +2907,38 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{"1948": 0.57, "1958": 0.52, "1967": 0.44, "1977": 0.5, "1989": 0.36}</t>
+          <t>{"1948": 0.57, "1958": 0.47, "1967": 0.44, "1977": 0.41, "1989": 0.36}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>v1.3_patch</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[0.1, 0.8]</t>
+          <t>DIV-015: corrected stale interpolated mid-year refvals 1958 (0.52-&gt;0.47) and 1977 (0.50-&gt;0.41) to book Table 5.5 'Lp/L' row values. 1948/1967/1989 unchanged (already book-correct).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>share_series</t>
+          <t>[0.1, 0.8]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2950,72 +2950,96 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>share_series</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tolerance_abs</t>
+          <t>tolerance_rel</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.05</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>source_table</t>
+          <t>tolerance_abs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Table 5.14, p.140</t>
+          <t>0.02</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>previous_1967_value</t>
+          <t>source_table</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>Table 5.14, p.140</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>previous_1967_source</t>
+          <t>previous_1967_value</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>code-derived (pre-v1.0, linear interpolation in Table5_7_KeyRatios.csv)</t>
+          <t>0.51</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>previous_1967_source</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>code-derived (pre-v1.0, linear interpolation in Table5_7_KeyRatios.csv)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>1967 midpoint anchor corrected from code-derived 0.51 to book Table 5.14 value 0.44. Endpoints 1948/1989 preserved from Table 5.7. Drift documented in DIV-006. Note: 1958/1977 intermediate values remain code-derived linear interpolations from Table 5.7 source CSV; only the 1967 midpoint has a directly-quoted book anchor in Table 5.14 (p.140).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
         </is>
       </c>
     </row>
